--- a/closes.xlsx
+++ b/closes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,162 +474,226 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B2" t="n">
-        <v>381.6000061035156</v>
+        <v>379.6600036621094</v>
       </c>
       <c r="C2" t="n">
-        <v>201.8600006103516</v>
+        <v>199.7700042724609</v>
       </c>
       <c r="D2" t="n">
-        <v>354.8337097167969</v>
+        <v>371.9171447753906</v>
       </c>
       <c r="E2" t="n">
-        <v>84.23000335693359</v>
+        <v>86.80000305175781</v>
       </c>
       <c r="F2" t="n">
-        <v>465.5799865722656</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="G2" t="n">
-        <v>346.3673706054688</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="H2" t="n">
-        <v>45.61000061035156</v>
+        <v>46.2599983215332</v>
       </c>
       <c r="I2" t="n">
-        <v>319.7000122070312</v>
+        <v>314.5799865722656</v>
       </c>
       <c r="J2" t="n">
-        <v>148.6999969482422</v>
+        <v>152.5128173828125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B3" t="n">
-        <v>379.3699951171875</v>
+        <v>381.6000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>206.1399993896484</v>
+        <v>201.8600006103516</v>
       </c>
       <c r="D3" t="n">
-        <v>349.6956481933594</v>
+        <v>354.8337097167969</v>
       </c>
       <c r="E3" t="n">
-        <v>84.88999938964844</v>
+        <v>84.23000335693359</v>
       </c>
       <c r="F3" t="n">
-        <v>470.7200012207031</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="G3" t="n">
-        <v>339.1320190429688</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="H3" t="n">
-        <v>45.33000183105469</v>
+        <v>45.61000061035156</v>
       </c>
       <c r="I3" t="n">
-        <v>316.8500061035156</v>
+        <v>319.7000122070312</v>
       </c>
       <c r="J3" t="n">
-        <v>148.7299957275391</v>
+        <v>148.6999969482422</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>372.6700134277344</v>
+        <v>379.3699951171875</v>
       </c>
       <c r="C4" t="n">
-        <v>211.0500030517578</v>
+        <v>206.1399993896484</v>
       </c>
       <c r="D4" t="n">
-        <v>335.3311767578125</v>
+        <v>349.6956481933594</v>
       </c>
       <c r="E4" t="n">
-        <v>81.84999847412109</v>
+        <v>84.88999938964844</v>
       </c>
       <c r="F4" t="n">
-        <v>459.6099853515625</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="G4" t="n">
-        <v>334.8047790527344</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="H4" t="n">
-        <v>45.11999893188477</v>
+        <v>45.33000183105469</v>
       </c>
       <c r="I4" t="n">
-        <v>325.1300048828125</v>
+        <v>316.8500061035156</v>
       </c>
       <c r="J4" t="n">
-        <v>145.5599975585938</v>
+        <v>148.7299957275391</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B5" t="n">
-        <v>378.3999938964844</v>
+        <v>372.6700134277344</v>
       </c>
       <c r="C5" t="n">
-        <v>211.7799987792969</v>
+        <v>211.0500030517578</v>
       </c>
       <c r="D5" t="n">
-        <v>341.4888305664062</v>
+        <v>335.3311767578125</v>
       </c>
       <c r="E5" t="n">
-        <v>80.93000030517578</v>
+        <v>81.84999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>457.0599975585938</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="G5" t="n">
-        <v>336.9034423828125</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="H5" t="n">
-        <v>46.77000045776367</v>
+        <v>45.11999893188477</v>
       </c>
       <c r="I5" t="n">
-        <v>324.9599914550781</v>
+        <v>325.1300048828125</v>
       </c>
       <c r="J5" t="n">
-        <v>144.1300048828125</v>
+        <v>145.5599975585938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B6" t="n">
+        <v>378.3999938964844</v>
+      </c>
+      <c r="C6" t="n">
+        <v>211.7799987792969</v>
+      </c>
+      <c r="D6" t="n">
+        <v>341.4888305664062</v>
+      </c>
+      <c r="E6" t="n">
+        <v>80.93000030517578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>457.0599975585938</v>
+      </c>
+      <c r="G6" t="n">
+        <v>336.9034423828125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>46.77000045776367</v>
+      </c>
+      <c r="I6" t="n">
+        <v>324.9599914550781</v>
+      </c>
+      <c r="J6" t="n">
+        <v>144.1300048828125</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>378.75</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>211.3200073242188</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>338.4599914550781</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>84.55999755859375</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>456.1600036621094</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>342.260009765625</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>47.5099983215332</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>328.2099914550781</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>375.0700073242188</v>
+      </c>
+      <c r="C8" t="n">
+        <v>208.6000061035156</v>
+      </c>
+      <c r="D8" t="n">
+        <v>357.0299987792969</v>
+      </c>
+      <c r="E8" t="n">
+        <v>89.36000061035156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>477.5700073242188</v>
+      </c>
+      <c r="G8" t="n">
+        <v>338.4599914550781</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46.59999847412109</v>
+      </c>
+      <c r="I8" t="n">
+        <v>319.9700012207031</v>
+      </c>
+      <c r="J8" t="n">
+        <v>154.3000030517578</v>
       </c>
     </row>
   </sheetData>
